--- a/artfynd/A 63857-2025 artfynd.xlsx
+++ b/artfynd/A 63857-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ4"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132901151</v>
+        <v>136707405</v>
       </c>
       <c r="B2" t="n">
-        <v>8449</v>
+        <v>92090</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,29 +691,24 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106554</v>
+        <v>4660</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hökeberg, Dls</t>
@@ -723,7 +718,7 @@
         <v>353122</v>
       </c>
       <c r="R2" t="n">
-        <v>6515553</v>
+        <v>6515561</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -766,6 +761,21 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -775,22 +785,22 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anton Larsson, Christine Bryngelsson</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132901151</t>
+          <t>https://artportalen.se/Sighting/136707405</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131126565</v>
+        <v>132901151</v>
       </c>
       <c r="B3" t="n">
-        <v>101325</v>
+        <v>8449</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,34 +808,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>106554</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hökeberg, Dls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>353237</v>
+        <v>353122</v>
       </c>
       <c r="R3" t="n">
-        <v>6515396</v>
+        <v>6515553</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -852,12 +867,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,22 +892,22 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Anton Larsson, Christine Bryngelsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131126565</t>
+          <t>https://artportalen.se/Sighting/132901151</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131126564</v>
+        <v>136707406</v>
       </c>
       <c r="B4" t="n">
-        <v>92632</v>
+        <v>8452</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3298</v>
+        <v>106554</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>353255</v>
+        <v>353125</v>
       </c>
       <c r="R4" t="n">
-        <v>6515401</v>
+        <v>6515526</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -954,12 +969,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -970,21 +985,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -999,6 +999,327 @@
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136707406</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>131126565</v>
+      </c>
+      <c r="B5" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Hökeberg, Dls</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>353237</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6515396</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Holm</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-01-29</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-01-29</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131126565</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>136707408</v>
+      </c>
+      <c r="B6" t="n">
+        <v>101556</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Hökeberg, Dls</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>353224</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6515455</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Holm</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136707408</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>131126564</v>
+      </c>
+      <c r="B7" t="n">
+        <v>92632</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Hökeberg, Dls</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>353255</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6515401</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Holm</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-01-29</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-01-29</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/131126564</t>
         </is>
@@ -1009,6 +1330,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 63857-2025 artfynd.xlsx
+++ b/artfynd/A 63857-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136707405</v>
       </c>
       <c r="B2" t="n">
-        <v>92090</v>
+        <v>92095</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>136707408</v>
       </c>
       <c r="B6" t="n">
-        <v>101556</v>
+        <v>101561</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 63857-2025 artfynd.xlsx
+++ b/artfynd/A 63857-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136707405</v>
       </c>
       <c r="B2" t="n">
-        <v>92095</v>
+        <v>92097</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>136707408</v>
       </c>
       <c r="B6" t="n">
-        <v>101561</v>
+        <v>101563</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 63857-2025 artfynd.xlsx
+++ b/artfynd/A 63857-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136707405</v>
       </c>
       <c r="B2" t="n">
-        <v>92097</v>
+        <v>92099</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>136707408</v>
       </c>
       <c r="B6" t="n">
-        <v>101563</v>
+        <v>101569</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 63857-2025 artfynd.xlsx
+++ b/artfynd/A 63857-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136707405</v>
       </c>
       <c r="B2" t="n">
-        <v>92099</v>
+        <v>92101</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>136707408</v>
       </c>
       <c r="B6" t="n">
-        <v>101569</v>
+        <v>101571</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 63857-2025 artfynd.xlsx
+++ b/artfynd/A 63857-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136707405</v>
       </c>
       <c r="B2" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>136707408</v>
       </c>
       <c r="B6" t="n">
-        <v>101571</v>
+        <v>101572</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 63857-2025 artfynd.xlsx
+++ b/artfynd/A 63857-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136707405</v>
       </c>
       <c r="B2" t="n">
-        <v>92102</v>
+        <v>92108</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>136707408</v>
       </c>
       <c r="B6" t="n">
-        <v>101572</v>
+        <v>101578</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 63857-2025 artfynd.xlsx
+++ b/artfynd/A 63857-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136707405</v>
       </c>
       <c r="B2" t="n">
-        <v>92108</v>
+        <v>92112</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>136707408</v>
       </c>
       <c r="B6" t="n">
-        <v>101578</v>
+        <v>101582</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 63857-2025 artfynd.xlsx
+++ b/artfynd/A 63857-2025 artfynd.xlsx
@@ -1111,7 +1111,7 @@
         <v>136707408</v>
       </c>
       <c r="B6" t="n">
-        <v>101582</v>
+        <v>101584</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 63857-2025 artfynd.xlsx
+++ b/artfynd/A 63857-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136707405</v>
       </c>
       <c r="B2" t="n">
-        <v>92112</v>
+        <v>92114</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>136707408</v>
       </c>
       <c r="B6" t="n">
-        <v>101584</v>
+        <v>101586</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 63857-2025 artfynd.xlsx
+++ b/artfynd/A 63857-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136707405</v>
       </c>
       <c r="B2" t="n">
-        <v>92114</v>
+        <v>92127</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>136707408</v>
       </c>
       <c r="B6" t="n">
-        <v>101586</v>
+        <v>101599</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 63857-2025 artfynd.xlsx
+++ b/artfynd/A 63857-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136707405</v>
       </c>
       <c r="B2" t="n">
-        <v>92127</v>
+        <v>92129</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136707406</v>
       </c>
       <c r="B4" t="n">
-        <v>8452</v>
+        <v>8453</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>136707408</v>
       </c>
       <c r="B6" t="n">
-        <v>101599</v>
+        <v>101601</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 63857-2025 artfynd.xlsx
+++ b/artfynd/A 63857-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136707405</v>
       </c>
       <c r="B2" t="n">
-        <v>92129</v>
+        <v>92132</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>136707408</v>
       </c>
       <c r="B6" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 63857-2025 artfynd.xlsx
+++ b/artfynd/A 63857-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136707405</v>
       </c>
       <c r="B2" t="n">
-        <v>92132</v>
+        <v>92142</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136707406</v>
       </c>
       <c r="B4" t="n">
-        <v>8453</v>
+        <v>8459</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>136707408</v>
       </c>
       <c r="B6" t="n">
-        <v>101604</v>
+        <v>101619</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
